--- a/data/trans_orig/P16A06-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A06-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>10537</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11218</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492167</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>494064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>456407</t>
+          <t>456952</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>465543</t>
+          <t>466409</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>950335</t>
+          <t>950868</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>959681</t>
+          <t>959832</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14737</t>
+          <t>14667</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21133</t>
+          <t>21392</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>724031</t>
+          <t>724285</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>733478</t>
+          <t>733566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>610757</t>
+          <t>610827</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>622513</t>
+          <t>622502</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1339849</t>
+          <t>1339590</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1354554</t>
+          <t>1354114</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15880</t>
+          <t>16209</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>9444</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24881</t>
+          <t>25743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15700</t>
+          <t>16128</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>36203</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>621769</t>
+          <t>621440</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633246</t>
+          <t>633250</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>664863</t>
+          <t>664001</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>680663</t>
+          <t>680300</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1291815</t>
+          <t>1291191</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1311694</t>
+          <t>1311266</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18595</t>
+          <t>18526</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13139</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30725</t>
+          <t>31233</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20812</t>
+          <t>21050</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43924</t>
+          <t>43335</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>500552</t>
+          <t>500621</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>515078</t>
+          <t>514733</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>484917</t>
+          <t>484409</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>502503</t>
+          <t>502365</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>990865</t>
+          <t>991454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1013977</t>
+          <t>1013739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17411</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16555</t>
+          <t>17793</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36483</t>
+          <t>37904</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25297</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50012</t>
+          <t>48351</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>369299</t>
+          <t>369187</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>382090</t>
+          <t>381686</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>367503</t>
+          <t>366082</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>387431</t>
+          <t>386193</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>740684</t>
+          <t>742345</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>765399</t>
+          <t>765934</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23064</t>
+          <t>22701</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>22785</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41606</t>
+          <t>43389</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35066</t>
+          <t>35168</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58702</t>
+          <t>58824</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>269519</t>
+          <t>269882</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283622</t>
+          <t>283585</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>301328</t>
+          <t>299545</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>322687</t>
+          <t>320149</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>576815</t>
+          <t>576693</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>600451</t>
+          <t>600349</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24941</t>
+          <t>25735</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23909</t>
+          <t>24404</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46563</t>
+          <t>47443</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37817</t>
+          <t>38897</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67638</t>
+          <t>66188</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>184942</t>
+          <t>184148</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200480</t>
+          <t>199582</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>287345</t>
+          <t>286465</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>309999</t>
+          <t>309504</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>476153</t>
+          <t>477603</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>505974</t>
+          <t>504894</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50520</t>
+          <t>50187</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80965</t>
+          <t>82874</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>116772</t>
+          <t>118361</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>164191</t>
+          <t>165057</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>180172</t>
+          <t>176275</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>235616</t>
+          <t>233535</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3194560</t>
+          <t>3192651</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3225005</t>
+          <t>3225338</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3215006</t>
+          <t>3214140</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3262425</t>
+          <t>3260836</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6419106</t>
+          <t>6421187</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6474550</t>
+          <t>6478447</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>13229</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449791</t>
+          <t>449310</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>417003</t>
+          <t>417006</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427359</t>
+          <t>427355</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>869081</t>
+          <t>869216</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>879638</t>
+          <t>879519</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15542</t>
+          <t>16159</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1633</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14093</t>
+          <t>14784</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24522</t>
+          <t>23161</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>670696</t>
+          <t>670079</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>684205</t>
+          <t>684230</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>595121</t>
+          <t>594430</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>607962</t>
+          <t>607581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1270929</t>
+          <t>1272290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1289612</t>
+          <t>1289533</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>8269</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26948</t>
+          <t>27982</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>22226</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43888</t>
+          <t>43708</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33095</t>
+          <t>34575</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60481</t>
+          <t>62754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>652076</t>
+          <t>651042</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>670902</t>
+          <t>670755</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>662047</t>
+          <t>662227</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>683982</t>
+          <t>683709</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1324478</t>
+          <t>1322205</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1351864</t>
+          <t>1350384</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>7314</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26322</t>
+          <t>24927</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22400</t>
+          <t>23279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47716</t>
+          <t>48239</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35575</t>
+          <t>34710</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65455</t>
+          <t>65891</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>588295</t>
+          <t>589690</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>607239</t>
+          <t>607303</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>565342</t>
+          <t>564819</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>590658</t>
+          <t>589779</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1162220</t>
+          <t>1161784</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1192100</t>
+          <t>1192965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18194</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23723</t>
+          <t>23290</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45676</t>
+          <t>46400</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31364</t>
+          <t>31406</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58356</t>
+          <t>57594</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>410150</t>
+          <t>410851</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>423145</t>
+          <t>423296</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>402124</t>
+          <t>401400</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>424077</t>
+          <t>424510</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>817788</t>
+          <t>818550</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>844780</t>
+          <t>844738</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>5143</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19619</t>
+          <t>19268</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29826</t>
+          <t>29251</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55082</t>
+          <t>52784</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37858</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67432</t>
+          <t>66919</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>288176</t>
+          <t>288527</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>302886</t>
+          <t>302652</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>297977</t>
+          <t>300275</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>323233</t>
+          <t>323808</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>593422</t>
+          <t>593935</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>622996</t>
+          <t>622107</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21395</t>
+          <t>20722</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58346</t>
+          <t>58017</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90508</t>
+          <t>90604</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69059</t>
+          <t>69921</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106984</t>
+          <t>106573</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>227424</t>
+          <t>228097</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241673</t>
+          <t>241767</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>296245</t>
+          <t>296149</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>328407</t>
+          <t>328736</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>528588</t>
+          <t>528999</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>566513</t>
+          <t>565651</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,0%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52781</t>
+          <t>54220</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90023</t>
+          <t>88623</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>192835</t>
+          <t>196652</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>254178</t>
+          <t>251511</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>258055</t>
+          <t>263880</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>326046</t>
+          <t>331559</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3327918</t>
+          <t>3329318</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3365160</t>
+          <t>3363721</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3290981</t>
+          <t>3293648</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3352324</t>
+          <t>3348507</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6637054</t>
+          <t>6631541</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6705045</t>
+          <t>6699220</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>11163</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>968</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>384335</t>
+          <t>384592</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394053</t>
+          <t>394762</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>804194</t>
+          <t>803201</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>814225</t>
+          <t>814250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12240</t>
+          <t>13050</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>15387</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>583476</t>
+          <t>584190</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>551304</t>
+          <t>550494</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>560762</t>
+          <t>560763</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1138889</t>
+          <t>1138653</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1149402</t>
+          <t>1149461</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13692</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23352</t>
+          <t>23384</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13153</t>
+          <t>13077</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30992</t>
+          <t>30395</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655405</t>
+          <t>655330</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667209</t>
+          <t>667245</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>638034</t>
+          <t>638002</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>653063</t>
+          <t>652347</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1299491</t>
+          <t>1300088</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1317330</t>
+          <t>1317406</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10528</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29379</t>
+          <t>28944</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>33271</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59953</t>
+          <t>60174</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49451</t>
+          <t>50230</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83169</t>
+          <t>83233</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>616669</t>
+          <t>617104</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>635520</t>
+          <t>634866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>589124</t>
+          <t>588903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>616152</t>
+          <t>615806</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1211956</t>
+          <t>1211892</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1245674</t>
+          <t>1244895</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28593</t>
+          <t>28910</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49959</t>
+          <t>52232</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84116</t>
+          <t>82213</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66691</t>
+          <t>65939</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103514</t>
+          <t>102934</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>449325</t>
+          <t>449008</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>467965</t>
+          <t>467658</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>414636</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>446890</t>
+          <t>444617</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>871253</t>
+          <t>871833</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>908076</t>
+          <t>908828</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>16383</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34543</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52933</t>
+          <t>52724</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82466</t>
+          <t>82553</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71574</t>
+          <t>73176</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108586</t>
+          <t>108239</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>299787</t>
+          <t>299647</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>318313</t>
+          <t>317947</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>295296</t>
+          <t>295209</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>324829</t>
+          <t>325038</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>603506</t>
+          <t>603853</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>640518</t>
+          <t>638916</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14788</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31379</t>
+          <t>31369</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48795</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80406</t>
+          <t>80657</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67948</t>
+          <t>65525</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>105150</t>
+          <t>102962</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225619</t>
+          <t>225629</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241971</t>
+          <t>242210</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>319763</t>
+          <t>319512</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>351374</t>
+          <t>352169</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>552017</t>
+          <t>554205</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>589219</t>
+          <t>591642</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>90,03%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73728</t>
+          <t>71362</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>112248</t>
+          <t>109099</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>234670</t>
+          <t>234505</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>297806</t>
+          <t>301382</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>318409</t>
+          <t>320372</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>399037</t>
+          <t>396633</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3282102</t>
+          <t>3285251</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3320622</t>
+          <t>3322988</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3246736</t>
+          <t>3243160</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3309872</t>
+          <t>3310037</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6539855</t>
+          <t>6542259</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6620483</t>
+          <t>6618520</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21602</t>
+          <t>23792</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27190</t>
+          <t>24140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32758</t>
+          <t>34378</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>378385</t>
+          <t>376195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286010</t>
+          <t>289060</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308136</t>
+          <t>308777</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>680429</t>
+          <t>678809</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>706570</t>
+          <t>706537</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>340</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15881</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19454</t>
+          <t>20043</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414844</t>
+          <t>414590</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423208</t>
+          <t>423207</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>495623</t>
+          <t>495835</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509014</t>
+          <t>508975</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>915597</t>
+          <t>915008</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>930303</t>
+          <t>930384</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26028</t>
+          <t>25874</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16029</t>
+          <t>16552</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32219</t>
+          <t>32467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26953</t>
+          <t>28522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49833</t>
+          <t>52620</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510310</t>
+          <t>510464</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>528188</t>
+          <t>528002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>510249</t>
+          <t>510001</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>526439</t>
+          <t>525916</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1028973</t>
+          <t>1026186</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1051853</t>
+          <t>1050284</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>11141</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48635</t>
+          <t>48230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44880</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75497</t>
+          <t>76035</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56988</t>
+          <t>53165</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116496</t>
+          <t>117211</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>839151</t>
+          <t>839556</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>876739</t>
+          <t>876645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>637224</t>
+          <t>636686</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>667841</t>
+          <t>666955</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1484011</t>
+          <t>1483296</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1543519</t>
+          <t>1547342</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27723</t>
+          <t>27681</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51049</t>
+          <t>51201</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>66408</t>
+          <t>67527</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91343</t>
+          <t>90962</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101339</t>
+          <t>99769</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134838</t>
+          <t>134619</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>509188</t>
+          <t>509036</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>532514</t>
+          <t>532556</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>453384</t>
+          <t>453765</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>478319</t>
+          <t>477200</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>970125</t>
+          <t>970344</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1003624</t>
+          <t>1005194</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,97%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24638</t>
+          <t>23341</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41562</t>
+          <t>41096</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28450</t>
+          <t>25041</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104172</t>
+          <t>102426</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51819</t>
+          <t>48130</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>128352</t>
+          <t>130055</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>326603</t>
+          <t>327069</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>343527</t>
+          <t>344824</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>504196</t>
+          <t>505942</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>579918</t>
+          <t>583327</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>848181</t>
+          <t>846478</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>924714</t>
+          <t>928403</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36592</t>
+          <t>36609</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55737</t>
+          <t>55997</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>103201</t>
+          <t>102633</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130033</t>
+          <t>128544</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>145326</t>
+          <t>145423</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>178260</t>
+          <t>177366</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>226532</t>
+          <t>226272</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245677</t>
+          <t>245660</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>294361</t>
+          <t>295850</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>321193</t>
+          <t>321761</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>528403</t>
+          <t>529297</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>561337</t>
+          <t>561240</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,42%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>131136</t>
+          <t>129731</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>196992</t>
+          <t>193911</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>304452</t>
+          <t>291033</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>401918</t>
+          <t>399005</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>455011</t>
+          <t>459592</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>578475</t>
+          <t>580537</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3261338</t>
+          <t>3264419</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3327194</t>
+          <t>3328599</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3255463</t>
+          <t>3258376</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3352929</t>
+          <t>3366348</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6537237</t>
+          <t>6535175</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6660701</t>
+          <t>6656120</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A06-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A06-Edad-trans_orig.xlsx
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10537</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>456952</t>
+          <t>456398</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>466409</t>
+          <t>465697</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>950868</t>
+          <t>950970</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>959832</t>
+          <t>959755</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11204</t>
+          <t>11518</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14667</t>
+          <t>14719</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21392</t>
+          <t>21570</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>724285</t>
+          <t>723971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>733566</t>
+          <t>733598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>610827</t>
+          <t>610775</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>622502</t>
+          <t>622622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1339590</t>
+          <t>1339412</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1354114</t>
+          <t>1353999</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16209</t>
+          <t>17166</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25743</t>
+          <t>24110</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>15319</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36203</t>
+          <t>35114</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>621440</t>
+          <t>620483</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633250</t>
+          <t>633344</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>664001</t>
+          <t>665634</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>680300</t>
+          <t>680539</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1291191</t>
+          <t>1292280</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1311266</t>
+          <t>1312075</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18526</t>
+          <t>19043</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13277</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31233</t>
+          <t>31477</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21050</t>
+          <t>21195</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43335</t>
+          <t>43416</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>500621</t>
+          <t>500104</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>514733</t>
+          <t>514845</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>484409</t>
+          <t>484165</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>502365</t>
+          <t>502907</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>991454</t>
+          <t>991373</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1013739</t>
+          <t>1013594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17523</t>
+          <t>18113</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,74 +2120,74 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>25956</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>17656</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>37493</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>9,28%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>35819</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>24737</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>48163</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>4,53%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>25956</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>17793</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>37904</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>35819</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>24762</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>48351</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
           <t>3,13%</t>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>369187</t>
+          <t>368597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>381686</t>
+          <t>381596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,77 +2233,77 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>95,32%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>378030</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>366493</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>386330</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>93,57%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>90,72%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>95,63%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>754877</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>742533</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>765959</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>95,47%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,7%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>378030</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>366082</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>386193</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,57%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>90,62%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>753</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>754877</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>742345</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>765934</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>95,47%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22701</t>
+          <t>22729</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22785</t>
+          <t>21597</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43389</t>
+          <t>42370</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35168</t>
+          <t>34406</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58824</t>
+          <t>59449</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>269882</t>
+          <t>269854</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283585</t>
+          <t>283629</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>299545</t>
+          <t>300564</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>320149</t>
+          <t>321337</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>576693</t>
+          <t>576068</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>600349</t>
+          <t>601111</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25735</t>
+          <t>26786</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24404</t>
+          <t>23827</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47443</t>
+          <t>47865</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>39156</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66188</t>
+          <t>67119</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>184148</t>
+          <t>183097</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>199582</t>
+          <t>199970</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>286465</t>
+          <t>286043</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>309504</t>
+          <t>310081</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>477603</t>
+          <t>476672</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>504894</t>
+          <t>504635</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50187</t>
+          <t>51342</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>82874</t>
+          <t>83533</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>118361</t>
+          <t>118772</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>165057</t>
+          <t>165490</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>176275</t>
+          <t>180315</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>233535</t>
+          <t>234048</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3192651</t>
+          <t>3191992</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3225338</t>
+          <t>3224183</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3214140</t>
+          <t>3213707</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3260836</t>
+          <t>3260425</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6421187</t>
+          <t>6420674</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6478447</t>
+          <t>6474407</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12333</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13229</t>
+          <t>14279</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449310</t>
+          <t>448545</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>417006</t>
+          <t>416879</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427355</t>
+          <t>427343</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>869216</t>
+          <t>868166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>879519</t>
+          <t>879593</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16159</t>
+          <t>15609</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14784</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23161</t>
+          <t>23658</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>670079</t>
+          <t>670629</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>684230</t>
+          <t>684272</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>594430</t>
+          <t>595205</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>607581</t>
+          <t>607587</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1272290</t>
+          <t>1271793</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1289533</t>
+          <t>1289854</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27982</t>
+          <t>28475</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>21676</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43708</t>
+          <t>44150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34575</t>
+          <t>33464</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62754</t>
+          <t>61700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>651042</t>
+          <t>650549</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>670755</t>
+          <t>670030</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>662227</t>
+          <t>661785</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>683709</t>
+          <t>684259</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1322205</t>
+          <t>1323259</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1350384</t>
+          <t>1351495</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24927</t>
+          <t>25312</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23279</t>
+          <t>22407</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48239</t>
+          <t>46301</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>35211</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65891</t>
+          <t>64912</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>589690</t>
+          <t>589305</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>607303</t>
+          <t>606256</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>564819</t>
+          <t>566757</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>589779</t>
+          <t>590651</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1161784</t>
+          <t>1162763</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1192965</t>
+          <t>1192464</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>16715</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23290</t>
+          <t>23899</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46400</t>
+          <t>46277</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31406</t>
+          <t>31738</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57594</t>
+          <t>58436</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>410851</t>
+          <t>411629</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>423296</t>
+          <t>423916</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>401400</t>
+          <t>401523</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>424510</t>
+          <t>423901</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>818550</t>
+          <t>817708</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>844738</t>
+          <t>844406</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19268</t>
+          <t>18914</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29251</t>
+          <t>29557</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52784</t>
+          <t>53694</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>37604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66919</t>
+          <t>66170</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>288527</t>
+          <t>288881</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>302652</t>
+          <t>302916</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>300275</t>
+          <t>299365</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>323808</t>
+          <t>323502</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>593935</t>
+          <t>594684</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>622107</t>
+          <t>623250</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20722</t>
+          <t>20815</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58017</t>
+          <t>58602</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90604</t>
+          <t>89048</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69921</t>
+          <t>68601</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106573</t>
+          <t>102672</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>228097</t>
+          <t>228004</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241767</t>
+          <t>242069</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>296149</t>
+          <t>297705</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>328736</t>
+          <t>328151</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>528999</t>
+          <t>532900</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>565651</t>
+          <t>566971</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54220</t>
+          <t>51830</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>88623</t>
+          <t>89358</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>196652</t>
+          <t>196237</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>251511</t>
+          <t>252201</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>263880</t>
+          <t>260782</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>331559</t>
+          <t>331267</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3329318</t>
+          <t>3328583</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3363721</t>
+          <t>3366111</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3293648</t>
+          <t>3292958</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3348507</t>
+          <t>3348922</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6631541</t>
+          <t>6631833</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6699220</t>
+          <t>6702318</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>12360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>384592</t>
+          <t>383456</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394762</t>
+          <t>394752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>803201</t>
+          <t>802858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>814250</t>
+          <t>813530</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13050</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>16139</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>584190</t>
+          <t>583540</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>550494</t>
+          <t>550428</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>560763</t>
+          <t>560781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1138653</t>
+          <t>1137901</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1149461</t>
+          <t>1149480</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13767</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23384</t>
+          <t>23275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13077</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30395</t>
+          <t>31104</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655330</t>
+          <t>655590</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667245</t>
+          <t>667242</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>638002</t>
+          <t>638111</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>652347</t>
+          <t>652842</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1300088</t>
+          <t>1299379</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1317406</t>
+          <t>1317237</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>11255</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28944</t>
+          <t>29398</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33271</t>
+          <t>33524</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60174</t>
+          <t>58051</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50230</t>
+          <t>48373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83233</t>
+          <t>81221</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>617104</t>
+          <t>616650</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>634866</t>
+          <t>634793</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>588903</t>
+          <t>591026</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>615806</t>
+          <t>615553</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1211892</t>
+          <t>1213904</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1244895</t>
+          <t>1246752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28910</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52232</t>
+          <t>51195</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82213</t>
+          <t>82631</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65939</t>
+          <t>67614</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102934</t>
+          <t>103983</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>449008</t>
+          <t>449172</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>467658</t>
+          <t>467818</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>414636</t>
+          <t>414218</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>444617</t>
+          <t>445654</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>871833</t>
+          <t>870784</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>908828</t>
+          <t>907153</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16383</t>
+          <t>16455</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34683</t>
+          <t>35260</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52724</t>
+          <t>51386</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82553</t>
+          <t>82021</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73176</t>
+          <t>74303</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108239</t>
+          <t>110299</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>299647</t>
+          <t>299070</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>317947</t>
+          <t>317875</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>295209</t>
+          <t>295741</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325038</t>
+          <t>326376</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>603853</t>
+          <t>601793</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>638916</t>
+          <t>637789</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14788</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31369</t>
+          <t>31899</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>46303</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80657</t>
+          <t>81133</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65525</t>
+          <t>68818</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102962</t>
+          <t>105243</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225629</t>
+          <t>225099</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>242210</t>
+          <t>242206</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>319512</t>
+          <t>319036</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>352169</t>
+          <t>353866</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>554205</t>
+          <t>551924</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>591642</t>
+          <t>588349</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>72586</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>109099</t>
+          <t>113046</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>234505</t>
+          <t>237364</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>301382</t>
+          <t>302058</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>320372</t>
+          <t>320580</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>396633</t>
+          <t>395757</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3285251</t>
+          <t>3281304</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3322988</t>
+          <t>3321764</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3243160</t>
+          <t>3242484</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3310037</t>
+          <t>3307178</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6542259</t>
+          <t>6543135</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6618520</t>
+          <t>6618312</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23792</t>
+          <t>18939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11740</t>
+          <t>12690</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24140</t>
+          <t>27253</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>17788</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34378</t>
+          <t>34240</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>395999</t>
+          <t>402695</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376195</t>
+          <t>388854</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>301460</t>
+          <t>349822</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289060</t>
+          <t>335259</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308777</t>
+          <t>357764</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>697459</t>
+          <t>752517</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>678809</t>
+          <t>736065</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>706537</t>
+          <t>762408</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8957</t>
+          <t>12301</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7470</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15669</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20043</t>
+          <t>23715</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>420736</t>
+          <t>471526</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414590</t>
+          <t>464589</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423207</t>
+          <t>475551</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>504301</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>495835</t>
+          <t>486043</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>508975</t>
+          <t>498224</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>925037</t>
+          <t>965139</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>915008</t>
+          <t>954258</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>930384</t>
+          <t>971724</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15205</t>
+          <t>15641</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25874</t>
+          <t>26390</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22665</t>
+          <t>25014</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32467</t>
+          <t>34301</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>37869</t>
+          <t>40655</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28522</t>
+          <t>29920</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52620</t>
+          <t>55575</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>521133</t>
+          <t>605196</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510464</t>
+          <t>594447</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>528002</t>
+          <t>612624</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>519803</t>
+          <t>597125</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>510001</t>
+          <t>587838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>525916</t>
+          <t>604169</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1040937</t>
+          <t>1202321</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1026186</t>
+          <t>1187401</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1050284</t>
+          <t>1213056</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30602</t>
+          <t>33185</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>23421</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48230</t>
+          <t>48429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>58499</t>
+          <t>56112</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45766</t>
+          <t>45157</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76035</t>
+          <t>68448</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>89101</t>
+          <t>89297</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53165</t>
+          <t>74648</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117211</t>
+          <t>107576</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>857184</t>
+          <t>667432</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>839556</t>
+          <t>652188</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>876645</t>
+          <t>677196</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>654222</t>
+          <t>680066</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>636686</t>
+          <t>667730</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>666955</t>
+          <t>691021</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1511406</t>
+          <t>1347498</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1483296</t>
+          <t>1329219</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1547342</t>
+          <t>1362147</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712721</t>
+          <t>736178</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712721</t>
+          <t>736178</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712721</t>
+          <t>736178</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600507</t>
+          <t>1436795</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600507</t>
+          <t>1436795</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600507</t>
+          <t>1436795</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>37866</t>
+          <t>39054</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27681</t>
+          <t>29400</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51201</t>
+          <t>51072</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>79077</t>
+          <t>87169</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67527</t>
+          <t>74786</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90962</t>
+          <t>102463</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>116943</t>
+          <t>126223</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99769</t>
+          <t>108775</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134619</t>
+          <t>144204</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>522371</t>
+          <t>569305</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>509036</t>
+          <t>557287</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>532556</t>
+          <t>578959</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>465650</t>
+          <t>519565</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>453765</t>
+          <t>504271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>477200</t>
+          <t>531948</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>988020</t>
+          <t>1088869</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>970344</t>
+          <t>1070888</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1005194</t>
+          <t>1106317</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544727</t>
+          <t>606734</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544727</t>
+          <t>606734</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544727</t>
+          <t>606734</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1104963</t>
+          <t>1215092</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1104963</t>
+          <t>1215092</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1104963</t>
+          <t>1215092</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,102 +11380,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>32160</t>
+          <t>34113</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23341</t>
+          <t>24881</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41096</t>
+          <t>43918</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>72967</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>61285</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>84235</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>16,62%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>13,95%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>19,18%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>107080</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>94443</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>122731</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>12,65%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>11,16%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>64861</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>25041</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>102426</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>10,66%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>16,84%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>97021</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>48130</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>130055</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -11493,102 +11493,102 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>336005</t>
+          <t>372967</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>327069</t>
+          <t>363162</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>344824</t>
+          <t>382199</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>89,21%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>93,89%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>366199</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>354931</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>377881</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>83,38%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>80,82%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>86,05%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>739166</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>723515</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>751803</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>87,35%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>85,5%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>88,84%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>93,66%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>543507</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>505942</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>583327</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>89,34%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>83,16%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>95,88%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1211</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>879512</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>846478</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>928403</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>90,06%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>86,68%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>45151</t>
+          <t>49317</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36609</t>
+          <t>39716</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55997</t>
+          <t>60783</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>115874</t>
+          <t>125807</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>102633</t>
+          <t>112130</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>128544</t>
+          <t>140096</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>161025</t>
+          <t>175124</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>145423</t>
+          <t>158202</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>177366</t>
+          <t>194251</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>237118</t>
+          <t>260386</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>226272</t>
+          <t>248920</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245660</t>
+          <t>269987</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>308520</t>
+          <t>337272</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>295850</t>
+          <t>322983</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>321761</t>
+          <t>350949</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>545638</t>
+          <t>597658</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>529297</t>
+          <t>578531</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>561240</t>
+          <t>614580</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,53%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>167783</t>
+          <t>181771</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>129731</t>
+          <t>158617</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>193911</t>
+          <t>210388</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>359919</t>
+          <t>387229</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>291033</t>
+          <t>357335</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>399005</t>
+          <t>418483</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>527702</t>
+          <t>569001</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>459592</t>
+          <t>529545</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>580537</t>
+          <t>610851</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3290547</t>
+          <t>3349509</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3264419</t>
+          <t>3320892</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3328599</t>
+          <t>3372663</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3297462</t>
+          <t>3343662</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3258376</t>
+          <t>3312408</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3366348</t>
+          <t>3373556</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6588010</t>
+          <t>6693169</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6535175</t>
+          <t>6651319</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6656120</t>
+          <t>6732625</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3657381</t>
+          <t>3730891</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3657381</t>
+          <t>3730891</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3657381</t>
+          <t>3730891</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7115712</t>
+          <t>7262170</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7115712</t>
+          <t>7262170</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7115712</t>
+          <t>7262170</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
